--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7aa5b980c12e4939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R913a9d19ba8d45bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R913a9d19ba8d45bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R94ca92f7d0754573"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R94ca92f7d0754573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bbb2fc26ae340b8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bbb2fc26ae340b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39708c659564491d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39708c659564491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra673ad020e584ddd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra673ad020e584ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R511d9efd45e94ed9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R511d9efd45e94ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dee9a8cb0814153"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dee9a8cb0814153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R917fb1b67ba348ac"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R917fb1b67ba348ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfab3e9995de3479c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfab3e9995de3479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R673d4b13af964d61"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R673d4b13af964d61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85077fc699014d18"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85077fc699014d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0f133c28cdc4976"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0f133c28cdc4976"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc75cd65d5f784b70"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc75cd65d5f784b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18717e34c6a94ab1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18717e34c6a94ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb762a044ffbe41ab"/>
   </x:sheets>
 </x:workbook>
 </file>
